--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.99</v>
+        <v>37.89</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.60673601764032</v>
+        <v>43.0021093559158</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.13769808621568</v>
+        <v>49.62613143190438</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2757173.109937037</v>
+        <v>1.087513037677982e-24</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50</v>
+        <v>1.97215226305253e-29</v>
       </c>
     </row>
   </sheetData>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>27.59149970738986</v>
+        <v>58.88774538866249</v>
       </c>
       <c r="F13" t="n">
-        <v>20.7079503524099</v>
+        <v>44.1963836980986</v>
       </c>
     </row>
     <row r="14">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>26.13769808621568</v>
+        <v>49.62613143190438</v>
       </c>
     </row>
     <row r="15">
@@ -1090,9 +1090,9 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.89890538496736</v>
+        <v>32.65640547673645</v>
       </c>
       <c r="C2" t="n">
-        <v>30.06383818154314</v>
+        <v>36.75897859574398</v>
       </c>
       <c r="D2" t="n">
-        <v>34.22877097811892</v>
+        <v>40.86155171475151</v>
       </c>
       <c r="E2" t="n">
-        <v>38.3937037746947</v>
+        <v>44.96412483375904</v>
       </c>
       <c r="F2" t="n">
-        <v>42.55863657127048</v>
+        <v>49.06669795276656</v>
       </c>
     </row>
     <row r="3">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.89890538496736</v>
+        <v>33.00523186990305</v>
       </c>
       <c r="C3" t="n">
-        <v>30.06383818154314</v>
+        <v>37.10780498891059</v>
       </c>
       <c r="D3" t="n">
-        <v>34.22877097811892</v>
+        <v>41.21037810791811</v>
       </c>
       <c r="E3" t="n">
-        <v>38.3937037746947</v>
+        <v>45.31295122692563</v>
       </c>
       <c r="F3" t="n">
-        <v>42.55863657127048</v>
+        <v>49.41552434593316</v>
       </c>
     </row>
     <row r="4">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.89890538496736</v>
+        <v>33.35405826306965</v>
       </c>
       <c r="C4" t="n">
-        <v>30.06383818154314</v>
+        <v>37.45663138207718</v>
       </c>
       <c r="D4" t="n">
-        <v>34.22877097811892</v>
+        <v>41.55920450108471</v>
       </c>
       <c r="E4" t="n">
-        <v>38.3937037746947</v>
+        <v>45.66177762009224</v>
       </c>
       <c r="F4" t="n">
-        <v>42.55863657127048</v>
+        <v>49.76435073909975</v>
       </c>
     </row>
     <row r="5">
@@ -1200,19 +1200,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.89890538496736</v>
+        <v>33.70288465623625</v>
       </c>
       <c r="C5" t="n">
-        <v>30.06383818154314</v>
+        <v>37.80545777524378</v>
       </c>
       <c r="D5" t="n">
-        <v>34.22877097811892</v>
+        <v>41.90803089425131</v>
       </c>
       <c r="E5" t="n">
-        <v>38.3937037746947</v>
+        <v>46.01060401325883</v>
       </c>
       <c r="F5" t="n">
-        <v>42.55863657127048</v>
+        <v>50.11317713226636</v>
       </c>
     </row>
     <row r="6">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.89890538496736</v>
+        <v>34.05171104940285</v>
       </c>
       <c r="C6" t="n">
-        <v>30.06383818154314</v>
+        <v>38.15428416841038</v>
       </c>
       <c r="D6" t="n">
-        <v>34.22877097811892</v>
+        <v>42.25685728741791</v>
       </c>
       <c r="E6" t="n">
-        <v>38.3937037746947</v>
+        <v>46.35943040642544</v>
       </c>
       <c r="F6" t="n">
-        <v>42.55863657127048</v>
+        <v>50.46200352543296</v>
       </c>
     </row>
   </sheetData>
@@ -1272,7 +1272,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>42.78</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="3">
@@ -1280,7 +1280,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>44.39</v>
+        <v>42.66</v>
       </c>
     </row>
     <row r="4">
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>44.92</v>
+        <v>42.72</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.89</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.79</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1294,35 +1293,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.74</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.087513037677982e-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.6</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.78</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43.0021093559158</v>
+        <v>43.06214240213441</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49.62613143190438</v>
+        <v>49.77621404745091</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62500</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60625</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.452922496800259</v>
+        <v>1.487879719021746</v>
       </c>
     </row>
     <row r="12">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62500</v>
+        <v>63000</v>
       </c>
       <c r="C2" t="n">
         <v>32571.42857142857</v>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60000</v>
+        <v>59500</v>
       </c>
       <c r="C4" t="n">
         <v>32571.42857142857</v>
       </c>
       <c r="D4" t="n">
-        <v>3.515194450335656</v>
+        <v>3.52504572321751</v>
       </c>
       <c r="E4" t="n">
         <v>0.625</v>
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58500</v>
+        <v>58000</v>
       </c>
       <c r="C5" t="n">
         <v>32571.42857142857</v>
       </c>
       <c r="D5" t="n">
-        <v>3.670806965853022</v>
+        <v>3.700213750574971</v>
       </c>
       <c r="E5" t="n">
         <v>0.625</v>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57000</v>
+        <v>56500</v>
       </c>
       <c r="C6" t="n">
         <v>32571.42857142857</v>
       </c>
       <c r="D6" t="n">
-        <v>3.818516873273591</v>
+        <v>3.855083651718663</v>
       </c>
       <c r="E6" t="n">
         <v>0.625</v>
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55500</v>
+        <v>54500</v>
       </c>
       <c r="C7" t="n">
         <v>32571.42857142857</v>
       </c>
       <c r="D7" t="n">
-        <v>3.902412706036639</v>
+        <v>3.950766393826274</v>
       </c>
       <c r="E7" t="n">
         <v>0.625</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54000</v>
+        <v>53000</v>
       </c>
       <c r="C8" t="n">
-        <v>33621.42857142857</v>
+        <v>33572.42857142857</v>
       </c>
       <c r="D8" t="n">
-        <v>4.097719306739934</v>
+        <v>4.132414349541416</v>
       </c>
       <c r="E8" t="n">
         <v>0.625</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52000</v>
+        <v>51500</v>
       </c>
       <c r="C9" t="n">
-        <v>33989.71428571429</v>
+        <v>33953.21428571429</v>
       </c>
       <c r="D9" t="n">
-        <v>4.285148797167985</v>
+        <v>4.306188917359129</v>
       </c>
       <c r="E9" t="n">
         <v>0.625</v>
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50000</v>
+        <v>49500</v>
       </c>
       <c r="C10" t="n">
-        <v>35970</v>
+        <v>35872.5</v>
       </c>
       <c r="D10" t="n">
-        <v>4.49479938112698</v>
+        <v>4.514857413971817</v>
       </c>
       <c r="E10" t="n">
         <v>0.625</v>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>58.88774538866249</v>
+        <v>59.08771710833847</v>
       </c>
       <c r="F13" t="n">
-        <v>44.1963836980986</v>
+        <v>44.34646631364512</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>49.62613143190438</v>
+        <v>49.77621404745091</v>
       </c>
     </row>
     <row r="15">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60625</v>
+        <v>60500</v>
       </c>
     </row>
   </sheetData>
@@ -1090,7 +1090,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.65640547673645</v>
+        <v>32.6962387075104</v>
       </c>
       <c r="C2" t="n">
-        <v>36.75897859574398</v>
+        <v>36.79881182651793</v>
       </c>
       <c r="D2" t="n">
-        <v>40.86155171475151</v>
+        <v>40.90138494552546</v>
       </c>
       <c r="E2" t="n">
-        <v>44.96412483375904</v>
+        <v>45.00395806453299</v>
       </c>
       <c r="F2" t="n">
-        <v>49.06669795276656</v>
+        <v>49.10653118354051</v>
       </c>
     </row>
     <row r="3">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.00523186990305</v>
+        <v>33.0536007929857</v>
       </c>
       <c r="C3" t="n">
-        <v>37.10780498891059</v>
+        <v>37.15617391199324</v>
       </c>
       <c r="D3" t="n">
-        <v>41.21037810791811</v>
+        <v>41.25874703100077</v>
       </c>
       <c r="E3" t="n">
-        <v>45.31295122692563</v>
+        <v>45.3613201500083</v>
       </c>
       <c r="F3" t="n">
-        <v>49.41552434593316</v>
+        <v>49.46389326901581</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.35405826306965</v>
+        <v>33.41096287846101</v>
       </c>
       <c r="C4" t="n">
-        <v>37.45663138207718</v>
+        <v>37.51353599746854</v>
       </c>
       <c r="D4" t="n">
-        <v>41.55920450108471</v>
+        <v>41.61610911647607</v>
       </c>
       <c r="E4" t="n">
-        <v>45.66177762009224</v>
+        <v>45.7186822354836</v>
       </c>
       <c r="F4" t="n">
-        <v>49.76435073909975</v>
+        <v>49.82125535449111</v>
       </c>
     </row>
     <row r="5">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.70288465623625</v>
+        <v>33.76832496393632</v>
       </c>
       <c r="C5" t="n">
-        <v>37.80545777524378</v>
+        <v>37.87089808294385</v>
       </c>
       <c r="D5" t="n">
-        <v>41.90803089425131</v>
+        <v>41.97347120195137</v>
       </c>
       <c r="E5" t="n">
-        <v>46.01060401325883</v>
+        <v>46.0760443209589</v>
       </c>
       <c r="F5" t="n">
-        <v>50.11317713226636</v>
+        <v>50.17861743996642</v>
       </c>
     </row>
     <row r="6">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.05171104940285</v>
+        <v>34.12568704941162</v>
       </c>
       <c r="C6" t="n">
-        <v>38.15428416841038</v>
+        <v>38.22826016841915</v>
       </c>
       <c r="D6" t="n">
-        <v>42.25685728741791</v>
+        <v>42.33083328742668</v>
       </c>
       <c r="E6" t="n">
-        <v>46.35943040642544</v>
+        <v>46.4334064064342</v>
       </c>
       <c r="F6" t="n">
-        <v>50.46200352543296</v>
+        <v>50.53597952544173</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1271,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>42.49</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="3">
@@ -1279,7 +1279,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>42.66</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="4">
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>42.72</v>
+        <v>42.78</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.11</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4828.902679265429</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.08659485508299977</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.44</v>
+        <v>40.06</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4828.902679265429</v>
+        <v>19341.02190413521</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08659485508299977</v>
+        <v>0.3468351093794434</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.06</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19341.02190413521</v>
+        <v>36896.00483744534</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3468351093794434</v>
+        <v>0.6616418686090109</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.81</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36896.00483744534</v>
+        <v>46960.86171920993</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6616418686090109</v>
+        <v>0.8421310772339647</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.24</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46960.86171920993</v>
+        <v>21681.68629524309</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8421310772339647</v>
+        <v>0.3888093439433833</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.16</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21681.68629524309</v>
+        <v>43683.93157165865</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3888093439433833</v>
+        <v>0.7833671488444445</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.1</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43683.93157165865</v>
+        <v>102434.6077884697</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7833671488444445</v>
+        <v>1.836920436399393</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.61</v>
+        <v>44.303</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>102434.6077884697</v>
+        <v>118655.4120188482</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.836920436399393</v>
+        <v>2.127801881927512</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.303</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>118655.4120188482</v>
+        <v>75048.83441250588</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.127801881927512</v>
+        <v>1.345821892001268</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43.06214240213441</v>
+        <v>45.50122844914844</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.58609463859008</v>
+        <v>41.2038421219884</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49.77621404745091</v>
+        <v>51.94730793988848</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.487879719021746</v>
+        <v>1.488043493831171</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75048.83441250588</v>
+        <v>16873.99841114706</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.345821892001268</v>
+        <v>0.3025085418905772</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1222.946666666666</v>
+        <v>1196.293333333333</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>529.4200000000001</v>
+        <v>515.39</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>404.9</v>
+        <v>499.049</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-64.849</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-657.8</v>
+        <v>-676.425</v>
       </c>
     </row>
     <row r="7">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>124.34</v>
       </c>
     </row>
     <row r="10">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1390.466666666666</v>
+        <v>1484.798333333333</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.58609463859008</v>
+        <v>41.2038421219884</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.58609463859008</v>
+        <v>41.2038421219884</v>
       </c>
     </row>
     <row r="14">
@@ -773,7 +773,7 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>59.08771710833847</v>
+        <v>61.98050637422234</v>
       </c>
       <c r="F13" t="n">
-        <v>44.34646631364512</v>
+        <v>46.5175602060827</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>49.77621404745091</v>
+        <v>51.94730793988848</v>
       </c>
     </row>
     <row r="15">
@@ -1090,7 +1090,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.6962387075104</v>
+        <v>35.3713389412334</v>
       </c>
       <c r="C2" t="n">
-        <v>36.79881182651793</v>
+        <v>39.37916405871205</v>
       </c>
       <c r="D2" t="n">
-        <v>40.90138494552546</v>
+        <v>43.38698917619068</v>
       </c>
       <c r="E2" t="n">
-        <v>45.00395806453299</v>
+        <v>47.39481429366934</v>
       </c>
       <c r="F2" t="n">
-        <v>49.10653118354051</v>
+        <v>51.40263941114797</v>
       </c>
     </row>
     <row r="3">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.0536007929857</v>
+        <v>35.72870102670871</v>
       </c>
       <c r="C3" t="n">
-        <v>37.15617391199324</v>
+        <v>39.73652614418735</v>
       </c>
       <c r="D3" t="n">
-        <v>41.25874703100077</v>
+        <v>43.74435126166598</v>
       </c>
       <c r="E3" t="n">
-        <v>45.3613201500083</v>
+        <v>47.75217637914464</v>
       </c>
       <c r="F3" t="n">
-        <v>49.46389326901581</v>
+        <v>51.76000149662327</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.41096287846101</v>
+        <v>36.08606311218401</v>
       </c>
       <c r="C4" t="n">
-        <v>37.51353599746854</v>
+        <v>40.09388822966265</v>
       </c>
       <c r="D4" t="n">
-        <v>41.61610911647607</v>
+        <v>44.10171334714128</v>
       </c>
       <c r="E4" t="n">
-        <v>45.7186822354836</v>
+        <v>48.10953846461994</v>
       </c>
       <c r="F4" t="n">
-        <v>49.82125535449111</v>
+        <v>52.11736358209858</v>
       </c>
     </row>
     <row r="5">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.76832496393632</v>
+        <v>36.44342519765931</v>
       </c>
       <c r="C5" t="n">
-        <v>37.87089808294385</v>
+        <v>40.45125031513796</v>
       </c>
       <c r="D5" t="n">
-        <v>41.97347120195137</v>
+        <v>44.45907543261659</v>
       </c>
       <c r="E5" t="n">
-        <v>46.0760443209589</v>
+        <v>48.46690055009525</v>
       </c>
       <c r="F5" t="n">
-        <v>50.17861743996642</v>
+        <v>52.47472566757388</v>
       </c>
     </row>
     <row r="6">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.12568704941162</v>
+        <v>36.80078728313462</v>
       </c>
       <c r="C6" t="n">
-        <v>38.22826016841915</v>
+        <v>40.80861240061326</v>
       </c>
       <c r="D6" t="n">
-        <v>42.33083328742668</v>
+        <v>44.8164375180919</v>
       </c>
       <c r="E6" t="n">
-        <v>46.4334064064342</v>
+        <v>48.82426263557056</v>
       </c>
       <c r="F6" t="n">
-        <v>50.53597952544173</v>
+        <v>52.83208775304918</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1271,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>42.55</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="3">
@@ -1279,7 +1279,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>42.72</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="4">
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>42.78</v>
+        <v>45.26</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.50122844914844</v>
+        <v>44.0165342099109</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51.94730793988848</v>
+        <v>50.57948241506342</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60500</v>
+        <v>61375</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.488043493831171</v>
+        <v>1.505089804682397</v>
       </c>
     </row>
     <row r="12">
@@ -552,7 +552,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16873.99841114706</v>
+        <v>41212.55564850164</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3025085418905772</v>
+        <v>0.7308256605263208</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +773,7 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63000</v>
+        <v>64000</v>
       </c>
       <c r="C2" t="n">
         <v>32571.42857142857</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61500</v>
+        <v>62250</v>
       </c>
       <c r="C3" t="n">
         <v>32571.42857142857</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59500</v>
+        <v>60500</v>
       </c>
       <c r="C4" t="n">
         <v>32571.42857142857</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58000</v>
+        <v>58750</v>
       </c>
       <c r="C5" t="n">
         <v>32571.42857142857</v>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56500</v>
+        <v>57000</v>
       </c>
       <c r="C6" t="n">
         <v>32571.42857142857</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54500</v>
+        <v>55250</v>
       </c>
       <c r="C7" t="n">
         <v>32571.42857142857</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53000</v>
+        <v>53500</v>
       </c>
       <c r="C8" t="n">
-        <v>33572.42857142857</v>
+        <v>33596.92857142857</v>
       </c>
       <c r="D8" t="n">
-        <v>4.132414349541416</v>
+        <v>4.134907101883459</v>
       </c>
       <c r="E8" t="n">
         <v>0.625</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51500</v>
+        <v>51750</v>
       </c>
       <c r="C9" t="n">
-        <v>33953.21428571429</v>
+        <v>33971.46428571429</v>
       </c>
       <c r="D9" t="n">
-        <v>4.306188917359129</v>
+        <v>4.308045763491466</v>
       </c>
       <c r="E9" t="n">
         <v>0.625</v>
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49500</v>
+        <v>50000</v>
       </c>
       <c r="C10" t="n">
-        <v>35872.5</v>
+        <v>35970</v>
       </c>
       <c r="D10" t="n">
-        <v>4.514857413971817</v>
+        <v>4.524777550843209</v>
       </c>
       <c r="E10" t="n">
         <v>0.625</v>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>61.98050637422234</v>
+        <v>60.15800067347929</v>
       </c>
       <c r="F13" t="n">
-        <v>46.5175602060827</v>
+        <v>45.14973468125763</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>51.94730793988848</v>
+        <v>50.57948241506342</v>
       </c>
     </row>
     <row r="15">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60500</v>
+        <v>61375</v>
       </c>
     </row>
   </sheetData>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.3713389412334</v>
+        <v>34.08955782081274</v>
       </c>
       <c r="C2" t="n">
-        <v>39.37916405871205</v>
+        <v>38.23722320168454</v>
       </c>
       <c r="D2" t="n">
-        <v>43.38698917619068</v>
+        <v>42.38488858255634</v>
       </c>
       <c r="E2" t="n">
-        <v>47.39481429366934</v>
+        <v>46.53255396342816</v>
       </c>
       <c r="F2" t="n">
-        <v>51.40263941114797</v>
+        <v>50.68021934429996</v>
       </c>
     </row>
     <row r="3">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.72870102670871</v>
+        <v>34.35773415427653</v>
       </c>
       <c r="C3" t="n">
-        <v>39.73652614418735</v>
+        <v>38.50539953514834</v>
       </c>
       <c r="D3" t="n">
-        <v>43.74435126166598</v>
+        <v>42.65306491602013</v>
       </c>
       <c r="E3" t="n">
-        <v>47.75217637914464</v>
+        <v>46.80073029689196</v>
       </c>
       <c r="F3" t="n">
-        <v>51.76000149662327</v>
+        <v>50.94839567776374</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.08606311218401</v>
+        <v>34.62591048774032</v>
       </c>
       <c r="C4" t="n">
-        <v>40.09388822966265</v>
+        <v>38.77357586861213</v>
       </c>
       <c r="D4" t="n">
-        <v>44.10171334714128</v>
+        <v>42.92124124948393</v>
       </c>
       <c r="E4" t="n">
-        <v>48.10953846461994</v>
+        <v>47.06890663035575</v>
       </c>
       <c r="F4" t="n">
-        <v>52.11736358209858</v>
+        <v>51.21657201122753</v>
       </c>
     </row>
     <row r="5">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.44342519765931</v>
+        <v>34.89408682120411</v>
       </c>
       <c r="C5" t="n">
-        <v>40.45125031513796</v>
+        <v>39.04175220207591</v>
       </c>
       <c r="D5" t="n">
-        <v>44.45907543261659</v>
+        <v>43.18941758294771</v>
       </c>
       <c r="E5" t="n">
-        <v>48.46690055009525</v>
+        <v>47.33708296381954</v>
       </c>
       <c r="F5" t="n">
-        <v>52.47472566757388</v>
+        <v>51.48474834469133</v>
       </c>
     </row>
     <row r="6">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.80078728313462</v>
+        <v>35.1622631546679</v>
       </c>
       <c r="C6" t="n">
-        <v>40.80861240061326</v>
+        <v>39.30992853553971</v>
       </c>
       <c r="D6" t="n">
-        <v>44.8164375180919</v>
+        <v>43.4575939164115</v>
       </c>
       <c r="E6" t="n">
-        <v>48.82426263557056</v>
+        <v>47.60525929728333</v>
       </c>
       <c r="F6" t="n">
-        <v>52.83208775304918</v>
+        <v>51.75292467815512</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1271,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>45.03</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="3">
@@ -1279,7 +1279,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>45.21</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="4">
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>45.26</v>
+        <v>43.79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.44</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41212.55564850164</v>
+        <v>3362.387328453808</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7308256605263208</v>
+        <v>0.05962549280420384</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.24</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3362.387328453808</v>
+        <v>32696.26777649092</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05962549280420384</v>
+        <v>0.5798056227888451</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.17</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32696.26777649092</v>
+        <v>131422.1234779493</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5798056227888451</v>
+        <v>2.330519393597371</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/gsl_fv_report.xlsx
+++ b/outputs/gsl_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.3</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>131422.1234779493</v>
+        <v>106819.5140699184</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.330519393597371</v>
+        <v>1.894239284577999</v>
       </c>
     </row>
   </sheetData>
